--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92988444977</v>
+        <v>46157.93075549795</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93075549795</v>
+        <v>46157.93348688329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93348688329</v>
+        <v>46157.93635272984</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93635272984</v>
+        <v>46158.28174043047</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28174043047</v>
+        <v>46158.29750283205</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>7.6</v>
+        <v>7.5</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92956256864</v>
+        <v>46158.29714912789</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>46157.86570978618</v>
       </c>
       <c r="H113" s="17" t="n">
-        <v>46157.92956256864</v>
+        <v>46158.29714912789</v>
       </c>
     </row>
     <row r="114" ht="135" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29750283205</v>
+        <v>46158.2976797547</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2976797547</v>
+        <v>46158.3044247565</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3044247565</v>
+        <v>46158.33337904468</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33337904468</v>
+        <v>46158.3719858797</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3719858797</v>
+        <v>46158.37410118629</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>7.5</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29714912789</v>
+        <v>46158.37370800905</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -52988,7 +52988,7 @@
         <v>46157.86570978618</v>
       </c>
       <c r="H113" s="17" t="n">
-        <v>46158.29714912789</v>
+        <v>46158.37370800905</v>
       </c>
     </row>
     <row r="114" ht="135" customHeight="1">
